--- a/Deliverables/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
+++ b/Deliverables/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Oliver-ARC\Deliverables\BOM\Fob_Transmitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14985732-85B3-4F41-BDDB-65800C67991F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6379AB4D-83CD-4ACA-B3D2-7134E5C3A453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5865" yWindow="3840" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13170" yWindow="240" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="249">
   <si>
     <t>Component list</t>
   </si>
@@ -47,30 +47,18 @@
     <t>#</t>
   </si>
   <si>
-    <t>Bill of Materials for Project [Fob_Transmitter.PrjPcb] (No PCB Document Selected)</t>
-  </si>
-  <si>
-    <t>Fob_Transmitter.PrjPcb</t>
-  </si>
-  <si>
     <t>None</t>
   </si>
   <si>
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C4, C6, C7, C11, C17, C18</t>
-  </si>
-  <si>
     <t>C2, C3</t>
   </si>
   <si>
     <t>C5</t>
   </si>
   <si>
-    <t>C8</t>
-  </si>
-  <si>
     <t>C9</t>
   </si>
   <si>
@@ -119,9 +107,6 @@
     <t>R1, R3, R4, R5, R10</t>
   </si>
   <si>
-    <t>R2</t>
-  </si>
-  <si>
     <t>R6</t>
   </si>
   <si>
@@ -140,9 +125,6 @@
     <t>R13</t>
   </si>
   <si>
-    <t>R14</t>
-  </si>
-  <si>
     <t>R17</t>
   </si>
   <si>
@@ -191,9 +173,6 @@
     <t>CAP CER 1UF 25V X5R 0603</t>
   </si>
   <si>
-    <t>CAP CER 0.1UF 50V X5R 0603</t>
-  </si>
-  <si>
     <t>CAP CER 10UF 6.3V X5R 0805</t>
   </si>
   <si>
@@ -239,9 +218,6 @@
     <t>RES SMD 10K OHM 5% 1/10W 0603</t>
   </si>
   <si>
-    <t>RES SMD 4.7K OHM 0.1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>RES SMD 220 OHM 1% 1/10W 0603</t>
   </si>
   <si>
@@ -392,9 +368,6 @@
     <t>CL10A105KA8NNNC</t>
   </si>
   <si>
-    <t>UMK107B104KAHT</t>
-  </si>
-  <si>
     <t>GRM21BR60J106KE19L</t>
   </si>
   <si>
@@ -404,9 +377,6 @@
     <t>CL10C180JB8NNNC</t>
   </si>
   <si>
-    <t>CC0603J*NPO9B*120</t>
-  </si>
-  <si>
     <t>0603CS-68NXJLW</t>
   </si>
   <si>
@@ -434,9 +404,6 @@
     <t>AC0603JR-0710KL</t>
   </si>
   <si>
-    <t>AT0603BRD074K7L</t>
-  </si>
-  <si>
     <t>RC0603FR-07220RL</t>
   </si>
   <si>
@@ -554,9 +521,6 @@
     <t>1uF</t>
   </si>
   <si>
-    <t>100nF</t>
-  </si>
-  <si>
     <t>10uF</t>
   </si>
   <si>
@@ -705,17 +669,126 @@
   </si>
   <si>
     <t>C2935993</t>
+  </si>
+  <si>
+    <t>C492404</t>
+  </si>
+  <si>
+    <t>C88374</t>
+  </si>
+  <si>
+    <t>C275404</t>
+  </si>
+  <si>
+    <t>C140867</t>
+  </si>
+  <si>
+    <t>C107696</t>
+  </si>
+  <si>
+    <t>C114618</t>
+  </si>
+  <si>
+    <t>C114668</t>
+  </si>
+  <si>
+    <t>C105578</t>
+  </si>
+  <si>
+    <t>C60491</t>
+  </si>
+  <si>
+    <t>C95177</t>
+  </si>
+  <si>
+    <t>C105428</t>
+  </si>
+  <si>
+    <t>C105588</t>
+  </si>
+  <si>
+    <t>C318893</t>
+  </si>
+  <si>
+    <t>C221841</t>
+  </si>
+  <si>
+    <t>C131975</t>
+  </si>
+  <si>
+    <t>C507118</t>
+  </si>
+  <si>
+    <t>C481380</t>
+  </si>
+  <si>
+    <t>C108704</t>
+  </si>
+  <si>
+    <t>C2715873</t>
+  </si>
+  <si>
+    <t>CC0603JRNPO9BN120</t>
+  </si>
+  <si>
+    <t>C107034</t>
+  </si>
+  <si>
+    <t>C527037</t>
+  </si>
+  <si>
+    <t>C965790</t>
+  </si>
+  <si>
+    <t>C492401</t>
+  </si>
+  <si>
+    <t>820nH</t>
+  </si>
+  <si>
+    <t>C1, C4, C6, C8, C7, C11, C17, C18</t>
+  </si>
+  <si>
+    <t>R2, R14</t>
+  </si>
+  <si>
+    <t>CC0603CRNPO0BN4R7</t>
+  </si>
+  <si>
+    <t>XL-1005SURC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Component Cost </t>
+  </si>
+  <si>
+    <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Need Custom Supplier Quotation</t>
+  </si>
+  <si>
+    <t>C5126754</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>Bill of Materials for Project [Fob_Transmitter.]</t>
+  </si>
+  <si>
+    <t>[Fob_Transmitter]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -861,8 +934,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -893,14 +998,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1145,12 +1244,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1305,6 +1430,63 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1329,53 +1511,13 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1719,7 +1861,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S51"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1753,15 +1895,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="59"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
+      <c r="O1" s="77"/>
+      <c r="P1" s="77"/>
+      <c r="Q1" s="77"/>
+      <c r="R1" s="77"/>
+      <c r="S1" s="78"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1772,7 +1914,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="54" t="s">
-        <v>5</v>
+        <v>247</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1797,7 +1939,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="55" t="s">
-        <v>6</v>
+        <v>248</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1811,7 +1953,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="60"/>
+      <c r="S3" s="79"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1822,7 +1964,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="56" t="s">
-        <v>6</v>
+        <v>248</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1836,7 +1978,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="61"/>
+      <c r="S4" s="80"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1847,7 +1989,7 @@
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="57" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" s="15"/>
       <c r="H5" s="6"/>
@@ -1861,7 +2003,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="61"/>
+      <c r="S5" s="80"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1882,7 +2024,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="61"/>
+      <c r="S6" s="80"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1903,7 +2045,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="61"/>
+      <c r="S7" s="80"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1924,7 +2066,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="61"/>
+      <c r="S8" s="80"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1932,55 +2074,55 @@
         <v>4</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D9" s="30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="L9" s="30" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="M9" s="30" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="N9" s="30" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="O9" s="30" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="P9" s="30" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="Q9" s="30" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="R9" s="32" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="S9" s="32" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1989,107 +2131,107 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="76" t="s">
-        <v>193</v>
-      </c>
-      <c r="D10" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="78" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="G10" s="78" t="s">
-        <v>117</v>
-      </c>
-      <c r="H10" s="77" t="s">
-        <v>150</v>
-      </c>
-      <c r="I10" s="77" t="s">
-        <v>206</v>
-      </c>
-      <c r="J10" s="77" t="s">
-        <v>216</v>
-      </c>
-      <c r="K10" s="78" t="s">
-        <v>171</v>
-      </c>
-      <c r="L10" s="77">
+      <c r="C10" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>238</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="I10" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J10" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="K10" s="47" t="s">
+        <v>160</v>
+      </c>
+      <c r="L10" s="46">
         <v>7</v>
       </c>
-      <c r="M10" s="78">
+      <c r="M10" s="47">
         <f>L10*5</f>
         <v>35</v>
       </c>
-      <c r="N10" s="77">
+      <c r="N10" s="46">
         <v>100</v>
       </c>
-      <c r="O10" s="79" t="s">
-        <v>217</v>
-      </c>
-      <c r="P10" s="80">
+      <c r="O10" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P10" s="52">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="Q10" s="80">
+      <c r="Q10" s="52">
         <f>P10*N10</f>
         <v>0.6</v>
       </c>
-      <c r="R10" s="81"/>
+      <c r="R10" s="48"/>
       <c r="S10" s="52"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="38">
-        <f t="shared" ref="B11:B49" si="0">ROW(B11) - ROW($B$9)</f>
+        <f t="shared" ref="B11:B47" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="67" t="s">
-        <v>193</v>
+      <c r="C11" s="59" t="s">
+        <v>181</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F11" s="49" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="H11" s="49" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I11" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J11" s="49" t="s">
         <v>206</v>
       </c>
-      <c r="J11" s="49" t="s">
-        <v>218</v>
-      </c>
       <c r="K11" s="50" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="L11" s="49">
         <v>2</v>
       </c>
       <c r="M11" s="50">
-        <f t="shared" ref="M11:M49" si="1">L11*5</f>
+        <f t="shared" ref="M11:M47" si="1">L11*5</f>
         <v>10</v>
       </c>
       <c r="N11" s="49">
         <v>20</v>
       </c>
-      <c r="O11" s="70" t="s">
-        <v>217</v>
+      <c r="O11" s="62" t="s">
+        <v>205</v>
       </c>
       <c r="P11" s="53">
         <v>3.2899999999999999E-2</v>
       </c>
       <c r="Q11" s="53">
-        <f t="shared" ref="Q11:Q49" si="2">P11*N11</f>
+        <f t="shared" ref="Q11:Q47" si="2">P11*N11</f>
         <v>0.65799999999999992</v>
       </c>
       <c r="R11" s="51"/>
@@ -2101,32 +2243,32 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="66" t="s">
-        <v>193</v>
+      <c r="C12" s="58" t="s">
+        <v>181</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="K12" s="47" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="L12" s="46">
         <v>1</v>
@@ -2138,8 +2280,8 @@
       <c r="N12" s="46">
         <v>50</v>
       </c>
-      <c r="O12" s="69" t="s">
-        <v>217</v>
+      <c r="O12" s="61" t="s">
+        <v>205</v>
       </c>
       <c r="P12" s="52">
         <v>4.1999999999999997E-3</v>
@@ -2154,804 +2296,887 @@
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B13) - ROW($B$9)</f>
         <v>4</v>
       </c>
-      <c r="C13" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="D13" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="72" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" s="73" t="s">
-        <v>120</v>
-      </c>
-      <c r="H13" s="72" t="s">
-        <v>151</v>
-      </c>
-      <c r="I13" s="72" t="s">
-        <v>206</v>
-      </c>
-      <c r="J13" s="72"/>
-      <c r="K13" s="73" t="s">
-        <v>174</v>
-      </c>
-      <c r="L13" s="72">
+      <c r="C13" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="H13" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="K13" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="L13" s="46">
         <v>1</v>
       </c>
-      <c r="M13" s="73">
+      <c r="M13" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="74"/>
-      <c r="Q13" s="74">
+      <c r="N13" s="46">
+        <v>20</v>
+      </c>
+      <c r="O13" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P13" s="52">
+        <v>2.69E-2</v>
+      </c>
+      <c r="Q13" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="75"/>
-      <c r="S13" s="53"/>
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="R13" s="48"/>
+      <c r="S13" s="52"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="38">
-        <f>ROW(B14) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="D14" s="46" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>92</v>
-      </c>
-      <c r="G14" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="H14" s="46" t="s">
-        <v>153</v>
-      </c>
-      <c r="I14" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J14" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="K14" s="47" t="s">
-        <v>175</v>
-      </c>
-      <c r="L14" s="46">
+      <c r="C14" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>209</v>
+      </c>
+      <c r="K14" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="L14" s="49">
         <v>1</v>
       </c>
-      <c r="M14" s="47">
+      <c r="M14" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N14" s="46">
-        <v>20</v>
-      </c>
-      <c r="O14" s="69" t="s">
-        <v>217</v>
-      </c>
-      <c r="P14" s="52">
-        <v>2.69E-2</v>
-      </c>
-      <c r="Q14" s="52">
+      <c r="N14" s="49">
+        <v>50</v>
+      </c>
+      <c r="O14" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P14" s="53">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="Q14" s="53">
         <f t="shared" si="2"/>
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="R14" s="48"/>
-      <c r="S14" s="52"/>
+        <v>0.28500000000000003</v>
+      </c>
+      <c r="R14" s="51"/>
+      <c r="S14" s="53"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B15) - ROW($B$9)</f>
         <v>6</v>
       </c>
-      <c r="C15" s="67" t="s">
-        <v>193</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J15" s="49" t="s">
-        <v>221</v>
-      </c>
-      <c r="K15" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="L15" s="49">
-        <v>1</v>
-      </c>
-      <c r="M15" s="50">
+      <c r="C15" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="I15" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J15" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="K15" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="L15" s="46">
+        <v>2</v>
+      </c>
+      <c r="M15" s="47">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N15" s="49">
+        <v>10</v>
+      </c>
+      <c r="N15" s="46">
         <v>50</v>
       </c>
-      <c r="O15" s="70" t="s">
-        <v>217</v>
-      </c>
-      <c r="P15" s="53">
-        <v>5.7000000000000002E-3</v>
-      </c>
-      <c r="Q15" s="53">
+      <c r="O15" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P15" s="52">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="Q15" s="52">
         <f t="shared" si="2"/>
-        <v>0.28500000000000003</v>
-      </c>
-      <c r="R15" s="51"/>
-      <c r="S15" s="53"/>
+        <v>0.4</v>
+      </c>
+      <c r="R15" s="48"/>
+      <c r="S15" s="52"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="38">
-        <f>ROW(B16) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="D16" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="47" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="46" t="s">
-        <v>154</v>
-      </c>
-      <c r="I16" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J16" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="K16" s="47" t="s">
-        <v>177</v>
-      </c>
-      <c r="L16" s="46">
-        <v>2</v>
-      </c>
-      <c r="M16" s="47">
+      <c r="C16" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>232</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>233</v>
+      </c>
+      <c r="K16" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="L16" s="49">
+        <v>1</v>
+      </c>
+      <c r="M16" s="50">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="N16" s="46">
-        <v>50</v>
-      </c>
-      <c r="O16" s="69" t="s">
-        <v>217</v>
-      </c>
-      <c r="P16" s="52">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="Q16" s="52">
+        <v>5</v>
+      </c>
+      <c r="N16" s="49">
+        <v>100</v>
+      </c>
+      <c r="O16" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P16" s="53">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q16" s="53">
         <f t="shared" si="2"/>
-        <v>0.4</v>
-      </c>
-      <c r="R16" s="48"/>
-      <c r="S16" s="52"/>
-    </row>
-    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="R16" s="51"/>
+      <c r="S16" s="53"/>
+    </row>
+    <row r="17" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="67" t="s">
-        <v>193</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="I17" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J17" s="49"/>
-      <c r="K17" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="L17" s="49">
+      <c r="C17" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J17" s="46"/>
+      <c r="K17" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="L17" s="46">
         <v>1</v>
       </c>
-      <c r="M17" s="50">
+      <c r="M17" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N17" s="49"/>
-      <c r="O17" s="49"/>
-      <c r="P17" s="53"/>
-      <c r="Q17" s="53">
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="52">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R17" s="51"/>
-      <c r="S17" s="53"/>
-    </row>
-    <row r="18" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R17" s="73" t="s">
+        <v>244</v>
+      </c>
+      <c r="S17" s="52"/>
+    </row>
+    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="38">
-        <f>ROW(B18) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="66" t="s">
-        <v>193</v>
-      </c>
-      <c r="D18" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="G18" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="I18" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J18" s="46"/>
-      <c r="K18" s="47" t="s">
-        <v>179</v>
-      </c>
-      <c r="L18" s="46">
+      <c r="C18" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="49" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="I18" s="49" t="s">
+        <v>240</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>234</v>
+      </c>
+      <c r="K18" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="L18" s="49">
         <v>1</v>
       </c>
-      <c r="M18" s="47">
+      <c r="M18" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="52"/>
-      <c r="Q18" s="52">
+      <c r="N18" s="49">
+        <v>50</v>
+      </c>
+      <c r="O18" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P18" s="53">
+        <v>8.8999999999999999E-3</v>
+      </c>
+      <c r="Q18" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="48"/>
-      <c r="S18" s="52"/>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="R18" s="51"/>
+      <c r="S18" s="53"/>
+    </row>
+    <row r="19" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="67" t="s">
-        <v>193</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="L19" s="49">
-        <v>1</v>
-      </c>
-      <c r="M19" s="50">
+      <c r="C19" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="G19" s="47" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J19" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="K19" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="L19" s="46">
+        <v>12</v>
+      </c>
+      <c r="M19" s="47">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53">
+        <v>60</v>
+      </c>
+      <c r="N19" s="46">
+        <v>80</v>
+      </c>
+      <c r="O19" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P19" s="52">
+        <v>2.58E-2</v>
+      </c>
+      <c r="Q19" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="51"/>
-      <c r="S19" s="53"/>
+        <v>2.0640000000000001</v>
+      </c>
+      <c r="R19" s="48"/>
+      <c r="S19" s="52"/>
     </row>
     <row r="20" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="38">
-        <f>ROW(B20) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="66" t="s">
-        <v>194</v>
-      </c>
-      <c r="D20" s="46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="F20" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" s="47" t="s">
-        <v>127</v>
-      </c>
-      <c r="H20" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="I20" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J20" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="K20" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="L20" s="46">
-        <v>12</v>
-      </c>
-      <c r="M20" s="47">
+      <c r="C20" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J20" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="K20" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="L20" s="49">
+        <v>1</v>
+      </c>
+      <c r="M20" s="50">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="N20" s="46">
-        <v>80</v>
-      </c>
-      <c r="O20" s="69" t="s">
-        <v>217</v>
-      </c>
-      <c r="P20" s="52">
-        <v>2.58E-2</v>
-      </c>
-      <c r="Q20" s="52">
+        <v>5</v>
+      </c>
+      <c r="N20" s="49">
+        <v>10</v>
+      </c>
+      <c r="O20" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P20" s="53">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="Q20" s="53">
         <f t="shared" si="2"/>
-        <v>2.0640000000000001</v>
-      </c>
-      <c r="R20" s="48"/>
-      <c r="S20" s="52"/>
-    </row>
-    <row r="21" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.52</v>
+      </c>
+      <c r="R20" s="51"/>
+      <c r="S20" s="53"/>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="67" t="s">
-        <v>195</v>
-      </c>
-      <c r="D21" s="49" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="F21" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G21" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="H21" s="49" t="s">
-        <v>157</v>
-      </c>
-      <c r="I21" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J21" s="49" t="s">
-        <v>224</v>
-      </c>
-      <c r="K21" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="L21" s="49">
+      <c r="C21" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" s="46" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J21" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="K21" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="L21" s="46">
         <v>1</v>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N21" s="49">
-        <v>10</v>
-      </c>
-      <c r="O21" s="70" t="s">
-        <v>217</v>
-      </c>
-      <c r="P21" s="53">
-        <v>5.1999999999999998E-2</v>
-      </c>
-      <c r="Q21" s="53">
+      <c r="N21" s="46">
+        <v>20</v>
+      </c>
+      <c r="O21" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P21" s="52">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="Q21" s="52">
         <f t="shared" si="2"/>
-        <v>0.52</v>
-      </c>
-      <c r="R21" s="51"/>
-      <c r="S21" s="53"/>
+        <v>0.53</v>
+      </c>
+      <c r="R21" s="48"/>
+      <c r="S21" s="52"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="38">
-        <f>ROW(B22) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="66" t="s">
-        <v>195</v>
-      </c>
-      <c r="D22" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="H22" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="I22" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J22" s="46"/>
-      <c r="K22" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="L22" s="46">
+      <c r="C22" s="59" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>214</v>
+      </c>
+      <c r="K22" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="L22" s="49">
         <v>1</v>
       </c>
-      <c r="M22" s="47">
+      <c r="M22" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N22" s="46"/>
-      <c r="O22" s="46"/>
-      <c r="P22" s="52"/>
-      <c r="Q22" s="52">
+      <c r="N22" s="49">
+        <v>10</v>
+      </c>
+      <c r="O22" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P22" s="53">
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="Q22" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="48"/>
-      <c r="S22" s="52"/>
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="R22" s="51"/>
+      <c r="S22" s="53"/>
     </row>
     <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="D23" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G23" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J23" s="49"/>
-      <c r="K23" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="L23" s="49">
+      <c r="C23" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="H23" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="I23" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J23" s="46" t="s">
+        <v>215</v>
+      </c>
+      <c r="K23" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="L23" s="46">
         <v>1</v>
       </c>
-      <c r="M23" s="50">
+      <c r="M23" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N23" s="49"/>
-      <c r="O23" s="49"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53">
+      <c r="N23" s="46">
+        <v>50</v>
+      </c>
+      <c r="O23" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P23" s="52">
+        <v>1.44E-2</v>
+      </c>
+      <c r="Q23" s="52">
+        <f t="shared" si="2"/>
+        <v>0.72</v>
+      </c>
+      <c r="R23" s="48"/>
+      <c r="S23" s="52"/>
+    </row>
+    <row r="24" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="38">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C24" s="59" t="s">
+        <v>185</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="I24" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J24" s="49"/>
+      <c r="K24" s="50" t="s">
+        <v>237</v>
+      </c>
+      <c r="L24" s="49">
+        <v>1</v>
+      </c>
+      <c r="M24" s="50">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="N24" s="49"/>
+      <c r="O24" s="49"/>
+      <c r="P24" s="53"/>
+      <c r="Q24" s="53">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R23" s="51"/>
-      <c r="S23" s="53"/>
-    </row>
-    <row r="24" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="38">
-        <f>ROW(B24) - ROW($B$9)</f>
-        <v>15</v>
-      </c>
-      <c r="C24" s="66" t="s">
-        <v>197</v>
-      </c>
-      <c r="D24" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="F24" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="H24" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="I24" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J24" s="46"/>
-      <c r="K24" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="L24" s="46">
+      <c r="R24" s="74" t="s">
+        <v>244</v>
+      </c>
+      <c r="S24" s="53"/>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="38">
+        <f>ROW(B25) - ROW($B$9)</f>
+        <v>16</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="J25" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="K25" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="L25" s="46">
         <v>1</v>
       </c>
-      <c r="M24" s="47">
+      <c r="M25" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N24" s="46"/>
-      <c r="O24" s="46"/>
-      <c r="P24" s="52"/>
-      <c r="Q24" s="52">
+      <c r="N25" s="46">
+        <v>100</v>
+      </c>
+      <c r="O25" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P25" s="52">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="Q25" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="48"/>
-      <c r="S24" s="52"/>
-    </row>
-    <row r="25" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="38">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C25" s="67" t="s">
-        <v>197</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="G25" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="I25" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J25" s="49"/>
-      <c r="K25" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="L25" s="49">
-        <v>1</v>
-      </c>
-      <c r="M25" s="50">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N25" s="49"/>
-      <c r="O25" s="49"/>
-      <c r="P25" s="53"/>
-      <c r="Q25" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="51"/>
-      <c r="S25" s="53"/>
+        <v>0.74</v>
+      </c>
+      <c r="R25" s="48"/>
+      <c r="S25" s="52"/>
     </row>
     <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="38">
-        <f>ROW(B26) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="66" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" s="46" t="s">
-        <v>99</v>
-      </c>
-      <c r="G26" s="47" t="s">
-        <v>132</v>
-      </c>
-      <c r="H26" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="I26" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J26" s="46"/>
-      <c r="K26" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="L26" s="46">
+      <c r="C26" s="59" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="G26" s="63">
+        <v>61300211121</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="I26" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>236</v>
+      </c>
+      <c r="K26" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="L26" s="49">
         <v>1</v>
       </c>
-      <c r="M26" s="47">
+      <c r="M26" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N26" s="46"/>
-      <c r="O26" s="46"/>
-      <c r="P26" s="52"/>
-      <c r="Q26" s="52">
+      <c r="N26" s="49">
+        <v>50</v>
+      </c>
+      <c r="O26" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P26" s="53">
+        <v>1.46E-2</v>
+      </c>
+      <c r="Q26" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="48"/>
-      <c r="S26" s="52"/>
+        <v>0.73</v>
+      </c>
+      <c r="R26" s="51"/>
+      <c r="S26" s="53"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="38">
-        <f t="shared" si="0"/>
+        <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="67" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="49" t="s">
-        <v>100</v>
-      </c>
-      <c r="G27" s="50">
-        <v>61300211121</v>
-      </c>
-      <c r="H27" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="I27" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J27" s="49"/>
-      <c r="K27" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="L27" s="49">
+      <c r="C27" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="G27" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J27" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="K27" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="L27" s="46">
         <v>1</v>
       </c>
-      <c r="M27" s="50">
+      <c r="M27" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N27" s="49"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="53"/>
-      <c r="Q27" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="51"/>
-      <c r="S27" s="53"/>
+      <c r="N27" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="O27" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="P27" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q27" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="R27" s="76" t="s">
+        <v>246</v>
+      </c>
+      <c r="S27" s="52"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="38">
-        <f>ROW(B28) - ROW($B$9)</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="66" t="s">
-        <v>199</v>
-      </c>
-      <c r="D28" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="G28" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J28" s="46"/>
-      <c r="K28" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="L28" s="46">
-        <v>1</v>
-      </c>
-      <c r="M28" s="47">
+      <c r="C28" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="D28" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="H28" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="I28" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="K28" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="L28" s="49">
+        <v>5</v>
+      </c>
+      <c r="M28" s="50">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="52"/>
-      <c r="Q28" s="52">
+        <v>25</v>
+      </c>
+      <c r="N28" s="49">
+        <v>100</v>
+      </c>
+      <c r="O28" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P28" s="53">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="Q28" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="48"/>
-      <c r="S28" s="52"/>
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="R28" s="51"/>
+      <c r="S28" s="53"/>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -2959,44 +3184,52 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="67" t="s">
-        <v>200</v>
+      <c r="C29" s="59" t="s">
+        <v>188</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F29" s="49" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G29" s="50" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H29" s="49" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I29" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J29" s="49"/>
+        <v>194</v>
+      </c>
+      <c r="J29" s="49" t="s">
+        <v>217</v>
+      </c>
       <c r="K29" s="50" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="L29" s="49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M29" s="50">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="N29" s="49"/>
-      <c r="O29" s="49"/>
-      <c r="P29" s="53"/>
+        <v>5</v>
+      </c>
+      <c r="N29" s="49">
+        <v>100</v>
+      </c>
+      <c r="O29" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P29" s="53">
+        <v>1.5E-3</v>
+      </c>
       <c r="Q29" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="53"/>
@@ -3007,30 +3240,32 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="66" t="s">
-        <v>200</v>
+      <c r="C30" s="58" t="s">
+        <v>188</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E30" s="47" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F30" s="46" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G30" s="47" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="H30" s="46" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I30" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J30" s="46"/>
+        <v>194</v>
+      </c>
+      <c r="J30" s="46" t="s">
+        <v>218</v>
+      </c>
       <c r="K30" s="47" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="L30" s="46">
         <v>1</v>
@@ -3039,12 +3274,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N30" s="46"/>
-      <c r="O30" s="46"/>
-      <c r="P30" s="52"/>
+      <c r="N30" s="46">
+        <v>100</v>
+      </c>
+      <c r="O30" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P30" s="52">
+        <v>1.2999999999999999E-3</v>
+      </c>
       <c r="Q30" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="R30" s="48"/>
       <c r="S30" s="52"/>
@@ -3055,44 +3296,52 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="67" t="s">
-        <v>200</v>
+      <c r="C31" s="59" t="s">
+        <v>188</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E31" s="50" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F31" s="49" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G31" s="50" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="H31" s="49" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I31" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J31" s="49"/>
+        <v>194</v>
+      </c>
+      <c r="J31" s="49" t="s">
+        <v>219</v>
+      </c>
       <c r="K31" s="50" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L31" s="49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M31" s="50">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N31" s="49"/>
-      <c r="O31" s="49"/>
-      <c r="P31" s="53"/>
+        <v>20</v>
+      </c>
+      <c r="N31" s="49">
+        <v>100</v>
+      </c>
+      <c r="O31" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P31" s="53">
+        <v>1.4E-3</v>
+      </c>
       <c r="Q31" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="53"/>
@@ -3103,30 +3352,32 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="66" t="s">
-        <v>200</v>
+      <c r="C32" s="58" t="s">
+        <v>188</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E32" s="47" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F32" s="46" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G32" s="47" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="H32" s="46" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I32" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J32" s="46"/>
+        <v>194</v>
+      </c>
+      <c r="J32" s="46" t="s">
+        <v>220</v>
+      </c>
       <c r="K32" s="47" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="L32" s="46">
         <v>1</v>
@@ -3135,12 +3386,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N32" s="46"/>
-      <c r="O32" s="46"/>
-      <c r="P32" s="52"/>
+      <c r="N32" s="46">
+        <v>100</v>
+      </c>
+      <c r="O32" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P32" s="52">
+        <v>1.4E-3</v>
+      </c>
       <c r="Q32" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.13999999999999999</v>
       </c>
       <c r="R32" s="48"/>
       <c r="S32" s="52"/>
@@ -3151,44 +3408,52 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="67" t="s">
-        <v>200</v>
+      <c r="C33" s="59" t="s">
+        <v>188</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E33" s="50" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F33" s="49" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G33" s="50" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H33" s="49" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I33" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J33" s="49"/>
+        <v>194</v>
+      </c>
+      <c r="J33" s="49" t="s">
+        <v>221</v>
+      </c>
       <c r="K33" s="50" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="L33" s="49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M33" s="50">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="N33" s="49"/>
-      <c r="O33" s="49"/>
-      <c r="P33" s="53"/>
+        <v>5</v>
+      </c>
+      <c r="N33" s="49">
+        <v>100</v>
+      </c>
+      <c r="O33" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P33" s="53">
+        <v>5.9999999999999995E-4</v>
+      </c>
       <c r="Q33" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="R33" s="51"/>
       <c r="S33" s="53"/>
@@ -3199,30 +3464,32 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="66" t="s">
-        <v>200</v>
+      <c r="C34" s="58" t="s">
+        <v>188</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="F34" s="46" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G34" s="47" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="H34" s="46" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I34" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J34" s="46"/>
+        <v>194</v>
+      </c>
+      <c r="J34" s="46" t="s">
+        <v>222</v>
+      </c>
       <c r="K34" s="47" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="L34" s="46">
         <v>1</v>
@@ -3231,12 +3498,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N34" s="46"/>
-      <c r="O34" s="46"/>
-      <c r="P34" s="52"/>
+      <c r="N34" s="46">
+        <v>100</v>
+      </c>
+      <c r="O34" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P34" s="52">
+        <v>1.1999999999999999E-3</v>
+      </c>
       <c r="Q34" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R34" s="48"/>
       <c r="S34" s="52"/>
@@ -3247,47 +3520,55 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="67" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="F35" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" s="50" t="s">
+      <c r="C35" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="D35" s="66" t="s">
+        <v>239</v>
+      </c>
+      <c r="E35" s="67" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="G35" s="67" t="s">
+        <v>130</v>
+      </c>
+      <c r="H35" s="66" t="s">
         <v>139</v>
       </c>
-      <c r="H35" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="I35" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J35" s="49"/>
-      <c r="K35" s="50" t="s">
-        <v>187</v>
-      </c>
-      <c r="L35" s="49">
+      <c r="I35" s="66" t="s">
+        <v>194</v>
+      </c>
+      <c r="J35" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="K35" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L35" s="66">
         <v>1</v>
       </c>
-      <c r="M35" s="50">
+      <c r="M35" s="67">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N35" s="49"/>
-      <c r="O35" s="49"/>
-      <c r="P35" s="53"/>
-      <c r="Q35" s="53">
+      <c r="N35" s="66">
+        <v>100</v>
+      </c>
+      <c r="O35" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="P35" s="69">
+        <v>1E-3</v>
+      </c>
+      <c r="Q35" s="69">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R35" s="51"/>
-      <c r="S35" s="53"/>
+        <v>0.1</v>
+      </c>
+      <c r="R35" s="70"/>
+      <c r="S35" s="69"/>
     </row>
     <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -3295,30 +3576,32 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="66" t="s">
-        <v>200</v>
+      <c r="C36" s="58" t="s">
+        <v>188</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E36" s="47" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="F36" s="46" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G36" s="47" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="H36" s="46" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="I36" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J36" s="46"/>
+        <v>194</v>
+      </c>
+      <c r="J36" s="46" t="s">
+        <v>224</v>
+      </c>
       <c r="K36" s="47" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="L36" s="46">
         <v>1</v>
@@ -3327,198 +3610,243 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N36" s="46"/>
-      <c r="O36" s="46"/>
-      <c r="P36" s="52"/>
+      <c r="N36" s="46">
+        <v>100</v>
+      </c>
+      <c r="O36" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P36" s="52">
+        <v>1E-3</v>
+      </c>
       <c r="Q36" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R36" s="48"/>
       <c r="S36" s="52"/>
     </row>
-    <row r="37" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="38">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="67" t="s">
-        <v>200</v>
+      <c r="C37" s="59" t="s">
+        <v>97</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E37" s="50" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F37" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="G37" s="50" t="s">
-        <v>141</v>
+        <v>192</v>
+      </c>
+      <c r="G37" s="49" t="s">
+        <v>97</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="I37" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J37" s="49"/>
+        <v>194</v>
+      </c>
+      <c r="J37" s="49" t="s">
+        <v>194</v>
+      </c>
       <c r="K37" s="50" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="L37" s="49">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="M37" s="50">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="53"/>
-      <c r="Q37" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R37" s="51"/>
+        <v>155</v>
+      </c>
+      <c r="N37" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="O37" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="P37" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q37" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="R37" s="75" t="s">
+        <v>246</v>
+      </c>
       <c r="S37" s="53"/>
     </row>
-    <row r="38" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="38">
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="66" t="s">
-        <v>200</v>
+      <c r="C38" s="58" t="s">
+        <v>189</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E38" s="47" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F38" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="G38" s="47" t="s">
-        <v>142</v>
+        <v>192</v>
+      </c>
+      <c r="G38" s="46" t="s">
+        <v>98</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I38" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J38" s="46"/>
+        <v>194</v>
+      </c>
+      <c r="J38" s="46" t="s">
+        <v>225</v>
+      </c>
       <c r="K38" s="47" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L38" s="46">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M38" s="47">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N38" s="46"/>
-      <c r="O38" s="46"/>
-      <c r="P38" s="52"/>
+        <v>45</v>
+      </c>
+      <c r="N38" s="46">
+        <v>50</v>
+      </c>
+      <c r="O38" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P38" s="52">
+        <v>6.3600000000000004E-2</v>
+      </c>
       <c r="Q38" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R38" s="48"/>
       <c r="S38" s="52"/>
     </row>
-    <row r="39" spans="1:19" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="38">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="67" t="s">
-        <v>105</v>
+      <c r="C39" s="59" t="s">
+        <v>189</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F39" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G39" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="H39" s="49"/>
+        <v>192</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="H39" s="49" t="s">
+        <v>153</v>
+      </c>
       <c r="I39" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J39" s="49"/>
-      <c r="K39" s="50"/>
+        <v>194</v>
+      </c>
+      <c r="J39" s="49" t="s">
+        <v>226</v>
+      </c>
+      <c r="K39" s="50" t="s">
+        <v>194</v>
+      </c>
       <c r="L39" s="49">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="M39" s="50">
         <f t="shared" si="1"/>
-        <v>155</v>
-      </c>
-      <c r="N39" s="49"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="53"/>
+        <v>5</v>
+      </c>
+      <c r="N39" s="49">
+        <v>6</v>
+      </c>
+      <c r="O39" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P39" s="53">
+        <v>0.47339999999999999</v>
+      </c>
       <c r="Q39" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2.8403999999999998</v>
       </c>
       <c r="R39" s="51"/>
       <c r="S39" s="53"/>
     </row>
-    <row r="40" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="38">
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="66" t="s">
-        <v>201</v>
+      <c r="C40" s="58" t="s">
+        <v>190</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E40" s="47" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F40" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="G40" s="46" t="s">
-        <v>106</v>
+        <v>100</v>
+      </c>
+      <c r="G40" s="47" t="s">
+        <v>132</v>
       </c>
       <c r="H40" s="46" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I40" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J40" s="46"/>
-      <c r="K40" s="47"/>
+        <v>194</v>
+      </c>
+      <c r="J40" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="K40" s="47" t="s">
+        <v>194</v>
+      </c>
       <c r="L40" s="46">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M40" s="47">
         <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="N40" s="46"/>
-      <c r="O40" s="46"/>
-      <c r="P40" s="52"/>
+        <v>5</v>
+      </c>
+      <c r="N40" s="46">
+        <v>6</v>
+      </c>
+      <c r="O40" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P40" s="52">
+        <v>0.78669999999999995</v>
+      </c>
       <c r="Q40" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4.7202000000000002</v>
       </c>
       <c r="R40" s="48"/>
       <c r="S40" s="52"/>
@@ -3529,29 +3857,33 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="67" t="s">
-        <v>201</v>
+      <c r="C41" s="59" t="s">
+        <v>190</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E41" s="50" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F41" s="49" t="s">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="G41" s="50" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="H41" s="49" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I41" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J41" s="49"/>
-      <c r="K41" s="50"/>
+        <v>194</v>
+      </c>
+      <c r="J41" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="K41" s="50" t="s">
+        <v>194</v>
+      </c>
       <c r="L41" s="49">
         <v>1</v>
       </c>
@@ -3559,42 +3891,48 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N41" s="49"/>
-      <c r="O41" s="49"/>
-      <c r="P41" s="53"/>
+      <c r="N41" s="49">
+        <v>6</v>
+      </c>
+      <c r="O41" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P41" s="53">
+        <v>0.95709999999999995</v>
+      </c>
       <c r="Q41" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.7425999999999995</v>
       </c>
       <c r="R41" s="51"/>
       <c r="S41" s="53"/>
     </row>
-    <row r="42" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="38">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="66" t="s">
-        <v>202</v>
+      <c r="C42" s="58" t="s">
+        <v>190</v>
       </c>
       <c r="D42" s="46" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E42" s="47" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F42" s="46" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G42" s="47" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="H42" s="46" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="I42" s="46" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="J42" s="46"/>
       <c r="K42" s="47"/>
@@ -3612,7 +3950,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R42" s="48"/>
+      <c r="R42" s="73" t="s">
+        <v>244</v>
+      </c>
       <c r="S42" s="52"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3621,29 +3961,33 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="67" t="s">
-        <v>202</v>
+      <c r="C43" s="59" t="s">
+        <v>190</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E43" s="50" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F43" s="49" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G43" s="50" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="H43" s="49" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="I43" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J43" s="49"/>
-      <c r="K43" s="50"/>
+        <v>194</v>
+      </c>
+      <c r="J43" s="49" t="s">
+        <v>229</v>
+      </c>
+      <c r="K43" s="50" t="s">
+        <v>194</v>
+      </c>
       <c r="L43" s="49">
         <v>1</v>
       </c>
@@ -3651,12 +3995,18 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N43" s="49"/>
-      <c r="O43" s="49"/>
-      <c r="P43" s="53"/>
+      <c r="N43" s="49">
+        <v>6</v>
+      </c>
+      <c r="O43" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P43" s="53">
+        <v>1.1791</v>
+      </c>
       <c r="Q43" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7.0746000000000002</v>
       </c>
       <c r="R43" s="51"/>
       <c r="S43" s="53"/>
@@ -3667,29 +4017,33 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="66" t="s">
-        <v>202</v>
+      <c r="C44" s="58" t="s">
+        <v>190</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E44" s="47" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F44" s="46" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="G44" s="47" t="s">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="H44" s="46" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="I44" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J44" s="46"/>
-      <c r="K44" s="47"/>
+        <v>194</v>
+      </c>
+      <c r="J44" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="K44" s="47" t="s">
+        <v>194</v>
+      </c>
       <c r="L44" s="46">
         <v>1</v>
       </c>
@@ -3697,42 +4051,46 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N44" s="46"/>
-      <c r="O44" s="46"/>
-      <c r="P44" s="52"/>
+      <c r="N44" s="46">
+        <v>6</v>
+      </c>
+      <c r="O44" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P44" s="52">
+        <v>2.8849999999999998</v>
+      </c>
       <c r="Q44" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="R44" s="48"/>
       <c r="S44" s="52"/>
     </row>
-    <row r="45" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="67" t="s">
-        <v>202</v>
+      <c r="C45" s="59" t="s">
+        <v>190</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E45" s="50" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F45" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="G45" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="H45" s="49" t="s">
-        <v>166</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G45" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="H45" s="49"/>
       <c r="I45" s="49" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="J45" s="49"/>
       <c r="K45" s="50"/>
@@ -3750,38 +4108,44 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R45" s="51"/>
+      <c r="R45" s="74" t="s">
+        <v>244</v>
+      </c>
       <c r="S45" s="53"/>
     </row>
-    <row r="46" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="38">
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="66" t="s">
-        <v>202</v>
+      <c r="C46" s="58" t="s">
+        <v>190</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F46" s="46" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="G46" s="47" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="H46" s="46" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="I46" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J46" s="46"/>
-      <c r="K46" s="47"/>
+        <v>194</v>
+      </c>
+      <c r="J46" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="K46" s="47" t="s">
+        <v>194</v>
+      </c>
       <c r="L46" s="46">
         <v>1</v>
       </c>
@@ -3789,214 +4153,174 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N46" s="46"/>
-      <c r="O46" s="46"/>
-      <c r="P46" s="52"/>
+      <c r="N46" s="46">
+        <v>10</v>
+      </c>
+      <c r="O46" s="61" t="s">
+        <v>205</v>
+      </c>
+      <c r="P46" s="52">
+        <v>0.11550000000000001</v>
+      </c>
       <c r="Q46" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.155</v>
       </c>
       <c r="R46" s="48"/>
       <c r="S46" s="52"/>
     </row>
-    <row r="47" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="38">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="67" t="s">
-        <v>202</v>
+      <c r="C47" s="59" t="s">
+        <v>191</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E47" s="50" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F47" s="49" t="s">
-        <v>204</v>
-      </c>
-      <c r="G47" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="H47" s="49"/>
+        <v>107</v>
+      </c>
+      <c r="G47" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="H47" s="49" t="s">
+        <v>159</v>
+      </c>
       <c r="I47" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J47" s="49"/>
-      <c r="K47" s="50"/>
-      <c r="L47" s="49">
+        <v>194</v>
+      </c>
+      <c r="J47" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="K47" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="L47" s="60">
         <v>1</v>
       </c>
       <c r="M47" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N47" s="49"/>
-      <c r="O47" s="49"/>
-      <c r="P47" s="53"/>
+      <c r="N47" s="49">
+        <v>10</v>
+      </c>
+      <c r="O47" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="P47" s="53">
+        <v>7.0000000000000007E-2</v>
+      </c>
       <c r="Q47" s="53">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="R47" s="51"/>
       <c r="S47" s="53"/>
     </row>
-    <row r="48" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="B48" s="38">
-        <f>ROW(B48) - ROW($B$9)</f>
-        <v>39</v>
-      </c>
-      <c r="C48" s="66" t="s">
-        <v>202</v>
-      </c>
-      <c r="D48" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="E48" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="F48" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="G48" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="H48" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="I48" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="J48" s="46"/>
-      <c r="K48" s="47"/>
-      <c r="L48" s="46">
-        <v>1</v>
-      </c>
-      <c r="M48" s="47">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N48" s="46"/>
-      <c r="O48" s="46"/>
-      <c r="P48" s="52"/>
-      <c r="Q48" s="52">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R48" s="48"/>
-      <c r="S48" s="52"/>
-    </row>
-    <row r="49" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="33"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="37"/>
+      <c r="L48" s="37"/>
+      <c r="M48" s="37"/>
+      <c r="N48" s="85" t="s">
+        <v>242</v>
+      </c>
+      <c r="O48" s="86"/>
+      <c r="P48" s="86"/>
+      <c r="Q48" s="71">
+        <f>SUM(Q10:Q47)</f>
+        <v>53.468800000000002</v>
+      </c>
+      <c r="R48" s="81"/>
+      <c r="S48" s="82"/>
+    </row>
+    <row r="49" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
-      <c r="B49" s="38">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C49" s="67" t="s">
-        <v>203</v>
-      </c>
-      <c r="D49" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="E49" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="F49" s="49" t="s">
-        <v>115</v>
-      </c>
-      <c r="G49" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="H49" s="49" t="s">
-        <v>170</v>
-      </c>
-      <c r="I49" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="J49" s="49"/>
-      <c r="K49" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="L49" s="68">
-        <v>1</v>
-      </c>
-      <c r="M49" s="50">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N49" s="49"/>
-      <c r="O49" s="49"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="53">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R49" s="51"/>
-      <c r="S49" s="53"/>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="44"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="36"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="36"/>
-      <c r="K50" s="37"/>
-      <c r="L50" s="37"/>
-      <c r="M50" s="37"/>
-      <c r="N50" s="37"/>
-      <c r="O50" s="37"/>
-      <c r="P50" s="37"/>
-      <c r="Q50" s="37"/>
-      <c r="R50" s="62"/>
-      <c r="S50" s="63"/>
-    </row>
-    <row r="51" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="64"/>
-      <c r="S51" s="65"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="85" t="s">
+        <v>243</v>
+      </c>
+      <c r="O49" s="86"/>
+      <c r="P49" s="86"/>
+      <c r="Q49" s="72">
+        <f>Q48/5</f>
+        <v>10.693760000000001</v>
+      </c>
+      <c r="R49" s="83"/>
+      <c r="S49" s="84"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R50:S51"/>
+    <mergeCell ref="R48:S49"/>
+    <mergeCell ref="N48:P48"/>
+    <mergeCell ref="N49:P49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1" xr:uid="{93FCBB62-42A6-4051-B5B2-E27EA6F0AB52}"/>
     <hyperlink ref="O11" r:id="rId2" xr:uid="{802626EB-2ACA-42F0-A805-8021786BE370}"/>
     <hyperlink ref="O12" r:id="rId3" xr:uid="{3EBC255E-892B-4E2B-ADDD-04CC4C060FDE}"/>
-    <hyperlink ref="O14" r:id="rId4" xr:uid="{939BC940-6CB2-408B-B1C5-957671D60377}"/>
-    <hyperlink ref="O15" r:id="rId5" xr:uid="{E41548EC-C50C-4397-88B6-5A455A5E14A9}"/>
-    <hyperlink ref="O16" r:id="rId6" xr:uid="{7517164D-2E08-4913-857F-890196B307A3}"/>
-    <hyperlink ref="O20" r:id="rId7" xr:uid="{3AC711A8-A387-4457-A729-88A9EB3EEE78}"/>
-    <hyperlink ref="O21" r:id="rId8" xr:uid="{147024DF-BC73-4730-AA60-5BAF0D015688}"/>
+    <hyperlink ref="O13" r:id="rId4" xr:uid="{939BC940-6CB2-408B-B1C5-957671D60377}"/>
+    <hyperlink ref="O14" r:id="rId5" xr:uid="{E41548EC-C50C-4397-88B6-5A455A5E14A9}"/>
+    <hyperlink ref="O15" r:id="rId6" xr:uid="{7517164D-2E08-4913-857F-890196B307A3}"/>
+    <hyperlink ref="O19" r:id="rId7" xr:uid="{3AC711A8-A387-4457-A729-88A9EB3EEE78}"/>
+    <hyperlink ref="O20" r:id="rId8" xr:uid="{147024DF-BC73-4730-AA60-5BAF0D015688}"/>
+    <hyperlink ref="O21" r:id="rId9" xr:uid="{FD6ECDA1-1122-4112-9730-82AE3225B61F}"/>
+    <hyperlink ref="O22" r:id="rId10" xr:uid="{267851DA-1A75-4CF3-AA5A-18368F7FE09C}"/>
+    <hyperlink ref="O23" r:id="rId11" xr:uid="{A7C5BF19-D9C1-4CB8-ADA1-C5B937E9473A}"/>
+    <hyperlink ref="O28" r:id="rId12" xr:uid="{527E0A18-CF11-43A5-9F7B-5B84A7D2566A}"/>
+    <hyperlink ref="O29" r:id="rId13" xr:uid="{B7F50116-4E91-4C71-BB00-7614AFE179FE}"/>
+    <hyperlink ref="O30" r:id="rId14" xr:uid="{11C22772-8AB6-4BD5-92F9-E9153E49E081}"/>
+    <hyperlink ref="O31" r:id="rId15" xr:uid="{7DFFB9D2-6EDD-436E-AB6C-A9307861FF73}"/>
+    <hyperlink ref="O32" r:id="rId16" xr:uid="{3176CD9D-5156-4007-B16F-F788973063E6}"/>
+    <hyperlink ref="O33" r:id="rId17" xr:uid="{7575416B-6563-4BF6-928B-AA3AC7370748}"/>
+    <hyperlink ref="O34" r:id="rId18" xr:uid="{9885186B-7D7A-472B-8B42-A3BD37B3E37E}"/>
+    <hyperlink ref="O35" r:id="rId19" xr:uid="{6DC81D02-E3C3-4D9B-BBDF-A2069D0F2C3C}"/>
+    <hyperlink ref="O36" r:id="rId20" xr:uid="{CF11E146-5D4B-4106-BD09-FB9ABD2C55FF}"/>
+    <hyperlink ref="O38" r:id="rId21" xr:uid="{FF039809-1F71-4955-80A3-1A16FB8C0395}"/>
+    <hyperlink ref="O39" r:id="rId22" xr:uid="{17B31971-CDC0-41D2-9B92-BE0F133B7AD1}"/>
+    <hyperlink ref="O40" r:id="rId23" xr:uid="{849D2452-4F85-4462-A648-5C223F0EF32D}"/>
+    <hyperlink ref="O41" r:id="rId24" xr:uid="{DD1CEA4A-37A2-4A26-AE73-6B3D917D5272}"/>
+    <hyperlink ref="O43" r:id="rId25" xr:uid="{EB299C28-D810-4413-A3CC-D2521FD032E5}"/>
+    <hyperlink ref="O46" r:id="rId26" xr:uid="{2A4EE5FE-7658-4070-A235-DCD8CC7A22EC}"/>
+    <hyperlink ref="O47" r:id="rId27" xr:uid="{3712FCF5-CA71-4144-A769-5B64AB4C5B64}"/>
+    <hyperlink ref="O16" r:id="rId28" xr:uid="{B3607444-DF02-42A4-8B2F-F333BB98177F}"/>
+    <hyperlink ref="O18" r:id="rId29" xr:uid="{8A4B66CA-0D62-4C22-A5E4-CB071D3C4809}"/>
+    <hyperlink ref="O25" r:id="rId30" xr:uid="{452B0F80-16E5-4FFA-9428-924C156E8624}"/>
+    <hyperlink ref="O26" r:id="rId31" xr:uid="{B9EB5940-084E-4A38-93CF-FDD074138881}"/>
+    <hyperlink ref="O44" r:id="rId32" xr:uid="{DE03E271-00A1-424A-B8B3-AB0F8F990DDE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
-  <drawing r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
 </worksheet>
 </file>
--- a/Deliverables/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
+++ b/Deliverables/BOM/Fob_Transmitter/eSpark_BOM_Fob_Transmitter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Oliver-ARC\Deliverables\BOM\Fob_Transmitter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6379AB4D-83CD-4ACA-B3D2-7134E5C3A453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B299F3-E443-451E-8041-656C72B1E5F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13170" yWindow="240" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5685" yWindow="1920" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="250">
   <si>
     <t>Component list</t>
   </si>
@@ -764,9 +764,6 @@
     <t>Single Board Cost</t>
   </si>
   <si>
-    <t>Need Custom Supplier Quotation</t>
-  </si>
-  <si>
     <t>C5126754</t>
   </si>
   <si>
@@ -777,6 +774,12 @@
   </si>
   <si>
     <t>[Fob_Transmitter]</t>
+  </si>
+  <si>
+    <t>LULU Quote</t>
+  </si>
+  <si>
+    <t>Custom Supplier</t>
   </si>
 </sst>
 </file>
@@ -788,7 +791,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -951,16 +954,7 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <strike/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -999,7 +993,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -1210,35 +1204,7 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1275,7 +1241,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1409,9 +1375,6 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1436,9 +1399,6 @@
     <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1451,40 +1411,16 @@
     <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1508,16 +1444,22 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1877,7 +1819,7 @@
     <col min="12" max="12" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
     <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
@@ -1895,15 +1837,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="78"/>
+      <c r="K1" s="67"/>
+      <c r="L1" s="67"/>
+      <c r="M1" s="67"/>
+      <c r="N1" s="67"/>
+      <c r="O1" s="67"/>
+      <c r="P1" s="67"/>
+      <c r="Q1" s="67"/>
+      <c r="R1" s="67"/>
+      <c r="S1" s="68"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1913,8 +1855,8 @@
         <v>0</v>
       </c>
       <c r="E2" s="11"/>
-      <c r="F2" s="54" t="s">
-        <v>247</v>
+      <c r="F2" s="53" t="s">
+        <v>246</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1938,8 +1880,8 @@
         <v>1</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="55" t="s">
-        <v>248</v>
+      <c r="F3" s="54" t="s">
+        <v>247</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1953,7 +1895,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="79"/>
+      <c r="S3" s="69"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1963,8 +1905,8 @@
         <v>2</v>
       </c>
       <c r="E4" s="13"/>
-      <c r="F4" s="56" t="s">
-        <v>248</v>
+      <c r="F4" s="55" t="s">
+        <v>247</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1978,7 +1920,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="80"/>
+      <c r="S4" s="70"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1988,7 +1930,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="13"/>
-      <c r="F5" s="57" t="s">
+      <c r="F5" s="56" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="15"/>
@@ -2003,7 +1945,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="80"/>
+      <c r="S5" s="70"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2024,7 +1966,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="80"/>
+      <c r="S6" s="70"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2045,7 +1987,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="80"/>
+      <c r="S7" s="70"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2066,7 +2008,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="80"/>
+      <c r="S8" s="70"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2131,7 +2073,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="57" t="s">
         <v>181</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -2168,18 +2110,18 @@
       <c r="N10" s="46">
         <v>100</v>
       </c>
-      <c r="O10" s="61" t="s">
+      <c r="O10" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P10" s="52">
+      <c r="P10" s="51">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="Q10" s="52">
+      <c r="Q10" s="51">
         <f>P10*N10</f>
         <v>0.6</v>
       </c>
       <c r="R10" s="48"/>
-      <c r="S10" s="52"/>
+      <c r="S10" s="51"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
@@ -2187,7 +2129,7 @@
         <f t="shared" ref="B11:B47" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="59" t="s">
+      <c r="C11" s="58" t="s">
         <v>181</v>
       </c>
       <c r="D11" s="49" t="s">
@@ -2224,18 +2166,18 @@
       <c r="N11" s="49">
         <v>20</v>
       </c>
-      <c r="O11" s="62" t="s">
+      <c r="O11" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P11" s="53">
+      <c r="P11" s="52">
         <v>3.2899999999999999E-2</v>
       </c>
-      <c r="Q11" s="53">
+      <c r="Q11" s="52">
         <f t="shared" ref="Q11:Q47" si="2">P11*N11</f>
         <v>0.65799999999999992</v>
       </c>
-      <c r="R11" s="51"/>
-      <c r="S11" s="53"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="49"/>
     </row>
     <row r="12" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
@@ -2243,7 +2185,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="57" t="s">
         <v>181</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -2280,18 +2222,18 @@
       <c r="N12" s="46">
         <v>50</v>
       </c>
-      <c r="O12" s="61" t="s">
+      <c r="O12" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P12" s="52">
+      <c r="P12" s="51">
         <v>4.1999999999999997E-3</v>
       </c>
-      <c r="Q12" s="52">
+      <c r="Q12" s="51">
         <f t="shared" si="2"/>
         <v>0.21</v>
       </c>
-      <c r="R12" s="48"/>
-      <c r="S12" s="52"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="46"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
@@ -2302,41 +2244,41 @@
       <c r="C13" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="47" t="s">
+      <c r="E13" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="H13" s="46" t="s">
+      <c r="H13" s="49" t="s">
         <v>142</v>
       </c>
-      <c r="I13" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J13" s="46" t="s">
+      <c r="I13" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J13" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="K13" s="47" t="s">
+      <c r="K13" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="L13" s="46">
+      <c r="L13" s="49">
         <v>1</v>
       </c>
-      <c r="M13" s="47">
+      <c r="M13" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N13" s="46">
+      <c r="N13" s="49">
         <v>20</v>
       </c>
-      <c r="O13" s="61" t="s">
+      <c r="O13" s="60" t="s">
         <v>205</v>
       </c>
       <c r="P13" s="52">
@@ -2346,8 +2288,8 @@
         <f t="shared" si="2"/>
         <v>0.53800000000000003</v>
       </c>
-      <c r="R13" s="48"/>
-      <c r="S13" s="52"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="49"/>
     </row>
     <row r="14" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -2355,55 +2297,55 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="50" t="s">
+      <c r="G14" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="H14" s="49" t="s">
+      <c r="H14" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="I14" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J14" s="49" t="s">
+      <c r="I14" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J14" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="K14" s="50" t="s">
+      <c r="K14" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="L14" s="49">
+      <c r="L14" s="46">
         <v>1</v>
       </c>
-      <c r="M14" s="50">
+      <c r="M14" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N14" s="49">
+      <c r="N14" s="46">
         <v>50</v>
       </c>
-      <c r="O14" s="62" t="s">
+      <c r="O14" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P14" s="53">
+      <c r="P14" s="51">
         <v>5.7000000000000002E-3</v>
       </c>
-      <c r="Q14" s="53">
+      <c r="Q14" s="51">
         <f t="shared" si="2"/>
         <v>0.28500000000000003</v>
       </c>
-      <c r="R14" s="51"/>
-      <c r="S14" s="53"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="46"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
@@ -2414,41 +2356,41 @@
       <c r="C15" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="47" t="s">
+      <c r="E15" s="50" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="49" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="47" t="s">
+      <c r="G15" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="46" t="s">
+      <c r="H15" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="I15" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J15" s="46" t="s">
+      <c r="I15" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J15" s="49" t="s">
         <v>210</v>
       </c>
-      <c r="K15" s="47" t="s">
+      <c r="K15" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="L15" s="46">
+      <c r="L15" s="49">
         <v>2</v>
       </c>
-      <c r="M15" s="47">
+      <c r="M15" s="50">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N15" s="46">
+      <c r="N15" s="49">
         <v>50</v>
       </c>
-      <c r="O15" s="61" t="s">
+      <c r="O15" s="60" t="s">
         <v>205</v>
       </c>
       <c r="P15" s="52">
@@ -2458,8 +2400,8 @@
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-      <c r="R15" s="48"/>
-      <c r="S15" s="52"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="49"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -2467,58 +2409,58 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="49" t="s">
+      <c r="F16" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="50" t="s">
+      <c r="G16" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="H16" s="49" t="s">
+      <c r="H16" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="I16" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J16" s="49" t="s">
+      <c r="I16" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J16" s="46" t="s">
         <v>233</v>
       </c>
-      <c r="K16" s="50" t="s">
+      <c r="K16" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="L16" s="49">
+      <c r="L16" s="46">
         <v>1</v>
       </c>
-      <c r="M16" s="50">
+      <c r="M16" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N16" s="49">
+      <c r="N16" s="46">
         <v>100</v>
       </c>
-      <c r="O16" s="62" t="s">
+      <c r="O16" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P16" s="53">
+      <c r="P16" s="51">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="Q16" s="53">
+      <c r="Q16" s="51">
         <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
-      <c r="R16" s="51"/>
-      <c r="S16" s="53"/>
-    </row>
-    <row r="17" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="46"/>
+    </row>
+    <row r="17" spans="1:19" s="78" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="77"/>
       <c r="B17" s="38">
         <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
@@ -2526,46 +2468,54 @@
       <c r="C17" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="50" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G17" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="H17" s="46" t="s">
+      <c r="H17" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="I17" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J17" s="46"/>
-      <c r="K17" s="47" t="s">
+      <c r="I17" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J17" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="K17" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="L17" s="46">
+      <c r="L17" s="49">
         <v>1</v>
       </c>
-      <c r="M17" s="47">
+      <c r="M17" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N17" s="46"/>
-      <c r="O17" s="46"/>
-      <c r="P17" s="52"/>
+      <c r="N17" s="49">
+        <v>7</v>
+      </c>
+      <c r="O17" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="P17" s="52">
+        <v>1.24</v>
+      </c>
       <c r="Q17" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="73" t="s">
-        <v>244</v>
-      </c>
-      <c r="S17" s="52"/>
+        <v>8.68</v>
+      </c>
+      <c r="R17" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="S17" s="49"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2573,55 +2523,55 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="59" t="s">
+      <c r="C18" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="47" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="49" t="s">
+      <c r="F18" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="63" t="s">
+      <c r="G18" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="H18" s="49" t="s">
+      <c r="H18" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="I18" s="49" t="s">
+      <c r="I18" s="46" t="s">
         <v>240</v>
       </c>
-      <c r="J18" s="49" t="s">
+      <c r="J18" s="46" t="s">
         <v>234</v>
       </c>
-      <c r="K18" s="50" t="s">
+      <c r="K18" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="L18" s="49">
+      <c r="L18" s="46">
         <v>1</v>
       </c>
-      <c r="M18" s="50">
+      <c r="M18" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N18" s="49">
+      <c r="N18" s="46">
         <v>50</v>
       </c>
-      <c r="O18" s="62" t="s">
+      <c r="O18" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P18" s="53">
+      <c r="P18" s="51">
         <v>8.8999999999999999E-3</v>
       </c>
-      <c r="Q18" s="53">
+      <c r="Q18" s="51">
         <f t="shared" si="2"/>
         <v>0.44500000000000001</v>
       </c>
-      <c r="R18" s="51"/>
-      <c r="S18" s="53"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="46"/>
     </row>
     <row r="19" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
@@ -2632,41 +2582,41 @@
       <c r="C19" s="58" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="47" t="s">
+      <c r="E19" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="46" t="s">
+      <c r="F19" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="47" t="s">
+      <c r="G19" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="H19" s="46" t="s">
+      <c r="H19" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="I19" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J19" s="46" t="s">
+      <c r="I19" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J19" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="K19" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="L19" s="46">
+      <c r="K19" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="L19" s="49">
         <v>12</v>
       </c>
-      <c r="M19" s="47">
+      <c r="M19" s="50">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="N19" s="46">
+      <c r="N19" s="49">
         <v>80</v>
       </c>
-      <c r="O19" s="61" t="s">
+      <c r="O19" s="60" t="s">
         <v>205</v>
       </c>
       <c r="P19" s="52">
@@ -2676,8 +2626,8 @@
         <f t="shared" si="2"/>
         <v>2.0640000000000001</v>
       </c>
-      <c r="R19" s="48"/>
-      <c r="S19" s="52"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="49"/>
     </row>
     <row r="20" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
@@ -2685,55 +2635,55 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="49" t="s">
+      <c r="F20" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="G20" s="50" t="s">
+      <c r="G20" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="H20" s="49" t="s">
+      <c r="H20" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="I20" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J20" s="49" t="s">
+      <c r="I20" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J20" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="K20" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="L20" s="49">
+      <c r="K20" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="L20" s="46">
         <v>1</v>
       </c>
-      <c r="M20" s="50">
+      <c r="M20" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N20" s="49">
+      <c r="N20" s="46">
         <v>10</v>
       </c>
-      <c r="O20" s="62" t="s">
+      <c r="O20" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P20" s="53">
+      <c r="P20" s="51">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="Q20" s="53">
+      <c r="Q20" s="51">
         <f t="shared" si="2"/>
         <v>0.52</v>
       </c>
-      <c r="R20" s="51"/>
-      <c r="S20" s="53"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="46"/>
     </row>
     <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
@@ -2744,41 +2694,41 @@
       <c r="C21" s="58" t="s">
         <v>183</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="46" t="s">
+      <c r="F21" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="H21" s="46" t="s">
+      <c r="H21" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="I21" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J21" s="46" t="s">
+      <c r="I21" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J21" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="K21" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="L21" s="46">
+      <c r="K21" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="L21" s="49">
         <v>1</v>
       </c>
-      <c r="M21" s="47">
+      <c r="M21" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N21" s="46">
+      <c r="N21" s="49">
         <v>20</v>
       </c>
-      <c r="O21" s="61" t="s">
+      <c r="O21" s="60" t="s">
         <v>205</v>
       </c>
       <c r="P21" s="52">
@@ -2788,8 +2738,8 @@
         <f t="shared" si="2"/>
         <v>0.53</v>
       </c>
-      <c r="R21" s="48"/>
-      <c r="S21" s="52"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="49"/>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
@@ -2797,55 +2747,55 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="49" t="s">
+      <c r="F22" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="G22" s="50" t="s">
+      <c r="G22" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="H22" s="49" t="s">
+      <c r="H22" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="I22" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J22" s="49" t="s">
+      <c r="I22" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J22" s="46" t="s">
         <v>214</v>
       </c>
-      <c r="K22" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="L22" s="49">
+      <c r="K22" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="L22" s="46">
         <v>1</v>
       </c>
-      <c r="M22" s="50">
+      <c r="M22" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N22" s="49">
+      <c r="N22" s="46">
         <v>10</v>
       </c>
-      <c r="O22" s="62" t="s">
+      <c r="O22" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P22" s="53">
+      <c r="P22" s="51">
         <v>8.9599999999999999E-2</v>
       </c>
-      <c r="Q22" s="53">
+      <c r="Q22" s="51">
         <f t="shared" si="2"/>
         <v>0.89600000000000002</v>
       </c>
-      <c r="R22" s="51"/>
-      <c r="S22" s="53"/>
+      <c r="R22" s="47"/>
+      <c r="S22" s="46"/>
     </row>
     <row r="23" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -2856,41 +2806,41 @@
       <c r="C23" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="47" t="s">
+      <c r="E23" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="46" t="s">
+      <c r="F23" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="G23" s="47" t="s">
+      <c r="G23" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="H23" s="46" t="s">
+      <c r="H23" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="I23" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J23" s="46" t="s">
+      <c r="I23" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J23" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="K23" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="L23" s="46">
+      <c r="K23" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="L23" s="49">
         <v>1</v>
       </c>
-      <c r="M23" s="47">
+      <c r="M23" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N23" s="46">
+      <c r="N23" s="49">
         <v>50</v>
       </c>
-      <c r="O23" s="61" t="s">
+      <c r="O23" s="60" t="s">
         <v>205</v>
       </c>
       <c r="P23" s="52">
@@ -2900,8 +2850,8 @@
         <f t="shared" si="2"/>
         <v>0.72</v>
       </c>
-      <c r="R23" s="48"/>
-      <c r="S23" s="52"/>
+      <c r="R23" s="50"/>
+      <c r="S23" s="49"/>
     </row>
     <row r="24" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
@@ -2909,49 +2859,57 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="57" t="s">
         <v>185</v>
       </c>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="50" t="s">
+      <c r="E24" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="49" t="s">
+      <c r="F24" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="50" t="s">
+      <c r="G24" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="H24" s="49" t="s">
+      <c r="H24" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J24" s="49"/>
-      <c r="K24" s="50" t="s">
+      <c r="I24" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J24" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="K24" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="L24" s="49">
+      <c r="L24" s="46">
         <v>1</v>
       </c>
-      <c r="M24" s="50">
+      <c r="M24" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N24" s="49"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53">
+      <c r="N24" s="46">
+        <v>7</v>
+      </c>
+      <c r="O24" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="P24" s="51">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Q24" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="74" t="s">
-        <v>244</v>
-      </c>
-      <c r="S24" s="53"/>
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="R24" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="S24" s="46"/>
     </row>
     <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
@@ -2962,41 +2920,41 @@
       <c r="C25" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="E25" s="47" t="s">
+      <c r="E25" s="50" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="F25" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="G25" s="64" t="s">
+      <c r="G25" s="61" t="s">
         <v>122</v>
       </c>
-      <c r="H25" s="46" t="s">
+      <c r="H25" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="I25" s="46" t="s">
+      <c r="I25" s="49" t="s">
         <v>241</v>
       </c>
-      <c r="J25" s="46" t="s">
+      <c r="J25" s="49" t="s">
         <v>235</v>
       </c>
-      <c r="K25" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="L25" s="46">
+      <c r="K25" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="L25" s="49">
         <v>1</v>
       </c>
-      <c r="M25" s="47">
+      <c r="M25" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N25" s="46">
+      <c r="N25" s="49">
         <v>100</v>
       </c>
-      <c r="O25" s="61" t="s">
+      <c r="O25" s="60" t="s">
         <v>205</v>
       </c>
       <c r="P25" s="52">
@@ -3006,8 +2964,8 @@
         <f t="shared" si="2"/>
         <v>0.74</v>
       </c>
-      <c r="R25" s="48"/>
-      <c r="S25" s="52"/>
+      <c r="R25" s="50"/>
+      <c r="S25" s="49"/>
     </row>
     <row r="26" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
@@ -3015,55 +2973,55 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="49" t="s">
+      <c r="D26" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="49" t="s">
+      <c r="F26" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="G26" s="63">
+      <c r="G26" s="47">
         <v>61300211121</v>
       </c>
-      <c r="H26" s="49" t="s">
+      <c r="H26" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="I26" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J26" s="49" t="s">
+      <c r="I26" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J26" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="K26" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="L26" s="49">
+      <c r="K26" s="47" t="s">
+        <v>194</v>
+      </c>
+      <c r="L26" s="46">
         <v>1</v>
       </c>
-      <c r="M26" s="50">
+      <c r="M26" s="47">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N26" s="49">
+      <c r="N26" s="46">
         <v>50</v>
       </c>
-      <c r="O26" s="62" t="s">
+      <c r="O26" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P26" s="53">
+      <c r="P26" s="51">
         <v>1.46E-2</v>
       </c>
-      <c r="Q26" s="53">
+      <c r="Q26" s="51">
         <f t="shared" si="2"/>
         <v>0.73</v>
       </c>
-      <c r="R26" s="51"/>
-      <c r="S26" s="53"/>
+      <c r="R26" s="47"/>
+      <c r="S26" s="46"/>
     </row>
     <row r="27" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
@@ -3074,41 +3032,41 @@
       <c r="C27" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="E27" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="F27" s="46" t="s">
+      <c r="E27" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="F27" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="G27" s="46" t="s">
+      <c r="G27" s="50" t="s">
         <v>93</v>
       </c>
-      <c r="H27" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="J27" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="K27" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="L27" s="46">
+      <c r="H27" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="K27" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="L27" s="49">
         <v>1</v>
       </c>
-      <c r="M27" s="47">
+      <c r="M27" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N27" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="O27" s="46" t="s">
+      <c r="N27" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="O27" s="60" t="s">
         <v>194</v>
       </c>
       <c r="P27" s="52" t="s">
@@ -3117,10 +3075,10 @@
       <c r="Q27" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="R27" s="76" t="s">
-        <v>246</v>
-      </c>
-      <c r="S27" s="52"/>
+      <c r="R27" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="S27" s="49"/>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
@@ -3128,55 +3086,55 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="59" t="s">
+      <c r="C28" s="57" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="49" t="s">
+      <c r="D28" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="50" t="s">
+      <c r="E28" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="49" t="s">
+      <c r="F28" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="50" t="s">
+      <c r="G28" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="H28" s="49" t="s">
+      <c r="H28" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="I28" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="J28" s="49" t="s">
+      <c r="I28" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="J28" s="46" t="s">
         <v>216</v>
       </c>
-      <c r="K28" s="50" t="s">
+      <c r="K28" s="47" t="s">
         <v>169</v>
       </c>
-      <c r="L28" s="49">
+      <c r="L28" s="46">
         <v>5</v>
       </c>
-      <c r="M28" s="50">
+      <c r="M28" s="47">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N28" s="49">
+      <c r="N28" s="46">
         <v>100</v>
       </c>
-      <c r="O28" s="62" t="s">
+      <c r="O28" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P28" s="53">
+      <c r="P28" s="51">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="Q28" s="53">
+      <c r="Q28" s="51">
         <f t="shared" si="2"/>
         <v>0.16999999999999998</v>
       </c>
-      <c r="R28" s="51"/>
-      <c r="S28" s="53"/>
+      <c r="R28" s="47"/>
+      <c r="S28" s="46"/>
     </row>
     <row r="29" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
@@ -3184,7 +3142,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="59" t="s">
+      <c r="C29" s="58" t="s">
         <v>188</v>
       </c>
       <c r="D29" s="49" t="s">
@@ -3221,18 +3179,18 @@
       <c r="N29" s="49">
         <v>100</v>
       </c>
-      <c r="O29" s="62" t="s">
+      <c r="O29" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P29" s="53">
+      <c r="P29" s="52">
         <v>1.5E-3</v>
       </c>
-      <c r="Q29" s="53">
+      <c r="Q29" s="52">
         <f t="shared" si="2"/>
         <v>0.15</v>
       </c>
-      <c r="R29" s="51"/>
-      <c r="S29" s="53"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="49"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -3240,7 +3198,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="57" t="s">
         <v>188</v>
       </c>
       <c r="D30" s="46" t="s">
@@ -3277,18 +3235,18 @@
       <c r="N30" s="46">
         <v>100</v>
       </c>
-      <c r="O30" s="61" t="s">
+      <c r="O30" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P30" s="52">
+      <c r="P30" s="51">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="Q30" s="52">
+      <c r="Q30" s="51">
         <f t="shared" si="2"/>
         <v>0.13</v>
       </c>
-      <c r="R30" s="48"/>
-      <c r="S30" s="52"/>
+      <c r="R30" s="47"/>
+      <c r="S30" s="46"/>
     </row>
     <row r="31" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -3296,7 +3254,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="59" t="s">
+      <c r="C31" s="58" t="s">
         <v>188</v>
       </c>
       <c r="D31" s="49" t="s">
@@ -3333,18 +3291,18 @@
       <c r="N31" s="49">
         <v>100</v>
       </c>
-      <c r="O31" s="62" t="s">
+      <c r="O31" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P31" s="53">
+      <c r="P31" s="52">
         <v>1.4E-3</v>
       </c>
-      <c r="Q31" s="53">
+      <c r="Q31" s="52">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R31" s="51"/>
-      <c r="S31" s="53"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="49"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -3352,7 +3310,7 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="57" t="s">
         <v>188</v>
       </c>
       <c r="D32" s="46" t="s">
@@ -3389,18 +3347,18 @@
       <c r="N32" s="46">
         <v>100</v>
       </c>
-      <c r="O32" s="61" t="s">
+      <c r="O32" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P32" s="52">
+      <c r="P32" s="51">
         <v>1.4E-3</v>
       </c>
-      <c r="Q32" s="52">
+      <c r="Q32" s="51">
         <f t="shared" si="2"/>
         <v>0.13999999999999999</v>
       </c>
-      <c r="R32" s="48"/>
-      <c r="S32" s="52"/>
+      <c r="R32" s="47"/>
+      <c r="S32" s="46"/>
     </row>
     <row r="33" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3408,7 +3366,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="58" t="s">
         <v>188</v>
       </c>
       <c r="D33" s="49" t="s">
@@ -3445,18 +3403,18 @@
       <c r="N33" s="49">
         <v>100</v>
       </c>
-      <c r="O33" s="62" t="s">
+      <c r="O33" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P33" s="53">
+      <c r="P33" s="52">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q33" s="53">
+      <c r="Q33" s="52">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="R33" s="51"/>
-      <c r="S33" s="53"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="49"/>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -3464,7 +3422,7 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="57" t="s">
         <v>188</v>
       </c>
       <c r="D34" s="46" t="s">
@@ -3501,18 +3459,18 @@
       <c r="N34" s="46">
         <v>100</v>
       </c>
-      <c r="O34" s="61" t="s">
+      <c r="O34" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P34" s="52">
+      <c r="P34" s="51">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q34" s="52">
+      <c r="Q34" s="51">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="R34" s="48"/>
-      <c r="S34" s="52"/>
+      <c r="R34" s="47"/>
+      <c r="S34" s="46"/>
     </row>
     <row r="35" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -3520,55 +3478,55 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="D35" s="66" t="s">
+      <c r="D35" s="49" t="s">
         <v>239</v>
       </c>
-      <c r="E35" s="67" t="s">
+      <c r="E35" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="F35" s="66" t="s">
+      <c r="F35" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="67" t="s">
+      <c r="G35" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="H35" s="66" t="s">
+      <c r="H35" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="I35" s="66" t="s">
-        <v>194</v>
-      </c>
-      <c r="J35" s="66" t="s">
+      <c r="I35" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J35" s="49" t="s">
         <v>223</v>
       </c>
-      <c r="K35" s="67" t="s">
+      <c r="K35" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="L35" s="66">
+      <c r="L35" s="49">
         <v>1</v>
       </c>
-      <c r="M35" s="67">
+      <c r="M35" s="50">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N35" s="66">
+      <c r="N35" s="49">
         <v>100</v>
       </c>
-      <c r="O35" s="68" t="s">
+      <c r="O35" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P35" s="69">
+      <c r="P35" s="52">
         <v>1E-3</v>
       </c>
-      <c r="Q35" s="69">
+      <c r="Q35" s="52">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="R35" s="70"/>
-      <c r="S35" s="69"/>
+      <c r="R35" s="50"/>
+      <c r="S35" s="49"/>
     </row>
     <row r="36" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
@@ -3576,7 +3534,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="58" t="s">
+      <c r="C36" s="57" t="s">
         <v>188</v>
       </c>
       <c r="D36" s="46" t="s">
@@ -3613,18 +3571,18 @@
       <c r="N36" s="46">
         <v>100</v>
       </c>
-      <c r="O36" s="61" t="s">
+      <c r="O36" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P36" s="52">
+      <c r="P36" s="51">
         <v>1E-3</v>
       </c>
-      <c r="Q36" s="52">
+      <c r="Q36" s="51">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="R36" s="48"/>
-      <c r="S36" s="52"/>
+      <c r="R36" s="47"/>
+      <c r="S36" s="46"/>
     </row>
     <row r="37" spans="1:19" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
@@ -3632,7 +3590,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="58" t="s">
         <v>97</v>
       </c>
       <c r="D37" s="49" t="s">
@@ -3644,7 +3602,7 @@
       <c r="F37" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="G37" s="49" t="s">
+      <c r="G37" s="50" t="s">
         <v>97</v>
       </c>
       <c r="H37" s="49" t="s">
@@ -3669,19 +3627,19 @@
       <c r="N37" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="O37" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="P37" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q37" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="R37" s="75" t="s">
-        <v>246</v>
-      </c>
-      <c r="S37" s="53"/>
+      <c r="O37" s="60" t="s">
+        <v>194</v>
+      </c>
+      <c r="P37" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q37" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="R37" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="S37" s="49"/>
     </row>
     <row r="38" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
@@ -3689,7 +3647,7 @@
         <f>ROW(B38) - ROW($B$9)</f>
         <v>29</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="C38" s="57" t="s">
         <v>189</v>
       </c>
       <c r="D38" s="46" t="s">
@@ -3701,7 +3659,7 @@
       <c r="F38" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="G38" s="46" t="s">
+      <c r="G38" s="47" t="s">
         <v>98</v>
       </c>
       <c r="H38" s="46" t="s">
@@ -3726,18 +3684,18 @@
       <c r="N38" s="46">
         <v>50</v>
       </c>
-      <c r="O38" s="61" t="s">
+      <c r="O38" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P38" s="52">
+      <c r="P38" s="51">
         <v>6.3600000000000004E-2</v>
       </c>
-      <c r="Q38" s="52">
+      <c r="Q38" s="51">
         <f t="shared" si="2"/>
         <v>3.18</v>
       </c>
-      <c r="R38" s="48"/>
-      <c r="S38" s="52"/>
+      <c r="R38" s="47"/>
+      <c r="S38" s="46"/>
     </row>
     <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
@@ -3745,7 +3703,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="58" t="s">
         <v>189</v>
       </c>
       <c r="D39" s="49" t="s">
@@ -3782,18 +3740,18 @@
       <c r="N39" s="49">
         <v>6</v>
       </c>
-      <c r="O39" s="62" t="s">
+      <c r="O39" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P39" s="53">
+      <c r="P39" s="52">
         <v>0.47339999999999999</v>
       </c>
-      <c r="Q39" s="53">
+      <c r="Q39" s="52">
         <f t="shared" si="2"/>
         <v>2.8403999999999998</v>
       </c>
-      <c r="R39" s="51"/>
-      <c r="S39" s="53"/>
+      <c r="R39" s="50"/>
+      <c r="S39" s="49"/>
     </row>
     <row r="40" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
@@ -3801,7 +3759,7 @@
         <f>ROW(B40) - ROW($B$9)</f>
         <v>31</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="57" t="s">
         <v>190</v>
       </c>
       <c r="D40" s="46" t="s">
@@ -3838,18 +3796,18 @@
       <c r="N40" s="46">
         <v>6</v>
       </c>
-      <c r="O40" s="61" t="s">
+      <c r="O40" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P40" s="52">
+      <c r="P40" s="51">
         <v>0.78669999999999995</v>
       </c>
-      <c r="Q40" s="52">
+      <c r="Q40" s="51">
         <f t="shared" si="2"/>
         <v>4.7202000000000002</v>
       </c>
-      <c r="R40" s="48"/>
-      <c r="S40" s="52"/>
+      <c r="R40" s="47"/>
+      <c r="S40" s="46"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
@@ -3857,7 +3815,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="C41" s="59" t="s">
+      <c r="C41" s="58" t="s">
         <v>190</v>
       </c>
       <c r="D41" s="49" t="s">
@@ -3894,26 +3852,26 @@
       <c r="N41" s="49">
         <v>6</v>
       </c>
-      <c r="O41" s="62" t="s">
+      <c r="O41" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P41" s="53">
+      <c r="P41" s="52">
         <v>0.95709999999999995</v>
       </c>
-      <c r="Q41" s="53">
+      <c r="Q41" s="52">
         <f t="shared" si="2"/>
         <v>5.7425999999999995</v>
       </c>
-      <c r="R41" s="51"/>
-      <c r="S41" s="53"/>
-    </row>
-    <row r="42" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R41" s="50"/>
+      <c r="S41" s="49"/>
+    </row>
+    <row r="42" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="38">
         <f>ROW(B42) - ROW($B$9)</f>
         <v>33</v>
       </c>
-      <c r="C42" s="58" t="s">
+      <c r="C42" s="57" t="s">
         <v>190</v>
       </c>
       <c r="D42" s="46" t="s">
@@ -3934,8 +3892,12 @@
       <c r="I42" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="J42" s="46"/>
-      <c r="K42" s="47"/>
+      <c r="J42" s="46" t="s">
+        <v>194</v>
+      </c>
+      <c r="K42" s="47" t="s">
+        <v>194</v>
+      </c>
       <c r="L42" s="46">
         <v>1</v>
       </c>
@@ -3943,17 +3905,23 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N42" s="46"/>
-      <c r="O42" s="46"/>
-      <c r="P42" s="52"/>
-      <c r="Q42" s="52">
+      <c r="N42" s="46">
+        <v>6</v>
+      </c>
+      <c r="O42" s="59" t="s">
+        <v>249</v>
+      </c>
+      <c r="P42" s="51">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="Q42" s="51">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R42" s="73" t="s">
-        <v>244</v>
-      </c>
-      <c r="S42" s="52"/>
+        <v>13.559999999999999</v>
+      </c>
+      <c r="R42" s="66" t="s">
+        <v>248</v>
+      </c>
+      <c r="S42" s="46"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -3961,7 +3929,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="C43" s="59" t="s">
+      <c r="C43" s="58" t="s">
         <v>190</v>
       </c>
       <c r="D43" s="49" t="s">
@@ -3998,18 +3966,18 @@
       <c r="N43" s="49">
         <v>6</v>
       </c>
-      <c r="O43" s="62" t="s">
+      <c r="O43" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P43" s="53">
+      <c r="P43" s="52">
         <v>1.1791</v>
       </c>
-      <c r="Q43" s="53">
+      <c r="Q43" s="52">
         <f t="shared" si="2"/>
         <v>7.0746000000000002</v>
       </c>
-      <c r="R43" s="51"/>
-      <c r="S43" s="53"/>
+      <c r="R43" s="50"/>
+      <c r="S43" s="49"/>
     </row>
     <row r="44" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -4017,7 +3985,7 @@
         <f>ROW(B44) - ROW($B$9)</f>
         <v>35</v>
       </c>
-      <c r="C44" s="58" t="s">
+      <c r="C44" s="57" t="s">
         <v>190</v>
       </c>
       <c r="D44" s="46" t="s">
@@ -4039,7 +4007,7 @@
         <v>194</v>
       </c>
       <c r="J44" s="46" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K44" s="47" t="s">
         <v>194</v>
@@ -4054,26 +4022,26 @@
       <c r="N44" s="46">
         <v>6</v>
       </c>
-      <c r="O44" s="61" t="s">
+      <c r="O44" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P44" s="52">
+      <c r="P44" s="51">
         <v>2.8849999999999998</v>
       </c>
-      <c r="Q44" s="52">
+      <c r="Q44" s="51">
         <f t="shared" si="2"/>
         <v>17.309999999999999</v>
       </c>
-      <c r="R44" s="48"/>
-      <c r="S44" s="52"/>
-    </row>
-    <row r="45" spans="1:19" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="R44" s="47"/>
+      <c r="S44" s="46"/>
+    </row>
+    <row r="45" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="38">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="C45" s="59" t="s">
+      <c r="C45" s="58" t="s">
         <v>190</v>
       </c>
       <c r="D45" s="49" t="s">
@@ -4085,15 +4053,21 @@
       <c r="F45" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="G45" s="49" t="s">
+      <c r="G45" s="50" t="s">
         <v>105</v>
       </c>
-      <c r="H45" s="49"/>
+      <c r="H45" s="49" t="s">
+        <v>194</v>
+      </c>
       <c r="I45" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="J45" s="49"/>
-      <c r="K45" s="50"/>
+      <c r="J45" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="K45" s="50" t="s">
+        <v>194</v>
+      </c>
       <c r="L45" s="49">
         <v>1</v>
       </c>
@@ -4101,17 +4075,23 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N45" s="49"/>
-      <c r="O45" s="49"/>
-      <c r="P45" s="53"/>
-      <c r="Q45" s="53">
+      <c r="N45" s="49">
+        <v>6</v>
+      </c>
+      <c r="O45" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="P45" s="52">
+        <v>3.28</v>
+      </c>
+      <c r="Q45" s="52">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R45" s="74" t="s">
-        <v>244</v>
-      </c>
-      <c r="S45" s="53"/>
+        <v>19.68</v>
+      </c>
+      <c r="R45" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="S45" s="49"/>
     </row>
     <row r="46" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
@@ -4119,7 +4099,7 @@
         <f>ROW(B46) - ROW($B$9)</f>
         <v>37</v>
       </c>
-      <c r="C46" s="58" t="s">
+      <c r="C46" s="57" t="s">
         <v>190</v>
       </c>
       <c r="D46" s="46" t="s">
@@ -4156,18 +4136,18 @@
       <c r="N46" s="46">
         <v>10</v>
       </c>
-      <c r="O46" s="61" t="s">
+      <c r="O46" s="59" t="s">
         <v>205</v>
       </c>
-      <c r="P46" s="52">
+      <c r="P46" s="51">
         <v>0.11550000000000001</v>
       </c>
-      <c r="Q46" s="52">
+      <c r="Q46" s="51">
         <f t="shared" si="2"/>
         <v>1.155</v>
       </c>
-      <c r="R46" s="48"/>
-      <c r="S46" s="52"/>
+      <c r="R46" s="47"/>
+      <c r="S46" s="46"/>
     </row>
     <row r="47" spans="1:19" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
@@ -4175,7 +4155,7 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="C47" s="59" t="s">
+      <c r="C47" s="58" t="s">
         <v>191</v>
       </c>
       <c r="D47" s="49" t="s">
@@ -4202,7 +4182,7 @@
       <c r="K47" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="L47" s="60">
+      <c r="L47" s="49">
         <v>1</v>
       </c>
       <c r="M47" s="50">
@@ -4212,18 +4192,18 @@
       <c r="N47" s="49">
         <v>10</v>
       </c>
-      <c r="O47" s="62" t="s">
+      <c r="O47" s="60" t="s">
         <v>205</v>
       </c>
-      <c r="P47" s="53">
+      <c r="P47" s="52">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="Q47" s="53">
+      <c r="Q47" s="52">
         <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="R47" s="51"/>
-      <c r="S47" s="53"/>
+      <c r="R47" s="50"/>
+      <c r="S47" s="49"/>
     </row>
     <row r="48" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
@@ -4239,17 +4219,17 @@
       <c r="K48" s="37"/>
       <c r="L48" s="37"/>
       <c r="M48" s="37"/>
-      <c r="N48" s="85" t="s">
+      <c r="N48" s="75" t="s">
         <v>242</v>
       </c>
-      <c r="O48" s="86"/>
-      <c r="P48" s="86"/>
-      <c r="Q48" s="71">
+      <c r="O48" s="76"/>
+      <c r="P48" s="76"/>
+      <c r="Q48" s="63">
         <f>SUM(Q10:Q47)</f>
-        <v>53.468800000000002</v>
-      </c>
-      <c r="R48" s="81"/>
-      <c r="S48" s="82"/>
+        <v>103.08880000000001</v>
+      </c>
+      <c r="R48" s="71"/>
+      <c r="S48" s="72"/>
     </row>
     <row r="49" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
@@ -4265,17 +4245,17 @@
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
       <c r="M49" s="10"/>
-      <c r="N49" s="85" t="s">
+      <c r="N49" s="75" t="s">
         <v>243</v>
       </c>
-      <c r="O49" s="86"/>
-      <c r="P49" s="86"/>
-      <c r="Q49" s="72">
+      <c r="O49" s="76"/>
+      <c r="P49" s="76"/>
+      <c r="Q49" s="64">
         <f>Q48/5</f>
-        <v>10.693760000000001</v>
-      </c>
-      <c r="R49" s="83"/>
-      <c r="S49" s="84"/>
+        <v>20.617760000000001</v>
+      </c>
+      <c r="R49" s="73"/>
+      <c r="S49" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="5">
